--- a/LubanConfig/Moba/Production/Datas/J-技能表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-技能表.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2111,6 +2111,534 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n">
+        <v>10070001</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>10070001</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>孙尚香-普通攻击</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>NormalAttack</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n">
+        <v>10070101</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>10070101</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>10070101</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>孙尚香-翻滚突袭</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n">
+        <v>10070201</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>10070201</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>10070201</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>孙尚香-红莲爆弹</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n">
+        <v>10070301</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>10070301</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>703</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>10070301</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>孙尚香-究极弩炮</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n">
+        <v>10070112</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>10070112</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>701</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>SunShangxiang Enhanced Basic Attack</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>NormalAttack</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n">
+        <v>10080001</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>10080001</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-普通攻击</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>NormalAttack</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n">
+        <v>10080101</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>10080101</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>10080101</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-河豚手雷</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n">
+        <v>10080201</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>10080201</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>802</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>10080201</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-无敌鲨嘴炮</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n">
+        <v>10080301</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>10080301</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>803</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>10080301</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-空中支援</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n">
+        <v>10080401</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>10080401</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>803</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>10080401</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-空中支援-召唤物投弹</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>RequiredTargetQueryId</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2122,7 +2650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2417,6 +2945,58 @@
       </c>
       <c r="H9" s="2" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>10070000</v>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>孙尚香-活力迸发</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10070000,10070002,10070003</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>ContinuousProcessIds</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n">
+        <v>10080000</v>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-火力压制</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10080002,10080003</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>ContinuousProcessIds</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2428,7 +3008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4288,6 +4868,202 @@
       <c r="F92" s="4" t="n"/>
       <c r="G92" s="4" t="n"/>
       <c r="H92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n"/>
+      <c r="B93" s="4" t="n">
+        <v>10070000</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>basicAttackCooldownResetMs</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>basicAttackCooldownResetMs</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n"/>
+      <c r="B94" s="4" t="n">
+        <v>10070101</v>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>180,8,450,400,2500,0.35,1500</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>damage,dashDistance,dashDurationMs,dashSpeed,enhancedWindowMs,enhancedAttackRatio,armorReductionDurationMs</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n"/>
+      <c r="B95" s="4" t="n">
+        <v>10070201</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>260,0.6,12,4,2000,0.35,1500</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>damage,physicalAttackRatio,range,radius,slowDurationMs,armorReductionPercent,armorReductionDurationMs</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n"/>
+      <c r="B96" s="4" t="n">
+        <v>10070301</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>360,1.0,18,500,3000</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>damage,physicalAttackRatio,range,projectileSpeed,damageFalloffPercent</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n"/>
+      <c r="B97" s="4" t="n">
+        <v>10080101</v>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>300,0.6,3.5,250,1000</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>damage,physicalAttackRatio,radius,delayMs,stunDurationMs</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n"/>
+      <c r="B98" s="4" t="n">
+        <v>10080201</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>500,1.0,30,25,500</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>damage,physicalAttackRatio,range,projectileSpeed,knockbackDurationMs</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n"/>
+      <c r="B99" s="4" t="n">
+        <v>10080301</v>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>1008,5000,5000,3</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>summonId,intervalMs,durationMs,totalCount</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n"/>
+      <c r="H99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n"/>
+      <c r="B100" s="4" t="n">
+        <v>10080401</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>80,0.5,12,20</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>damage,physicalAttackRatio,range,projectileSpeed</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H91"/>

--- a/LubanConfig/Moba/Production/Datas/J-技能表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-技能表.xlsx
@@ -452,8 +452,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -560,6 +560,11 @@
           <t>ExecutionBlockedFlagIds</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>PreviewVfxId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -647,6 +652,11 @@
           <t>(list#sep=,),int</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -732,6 +742,11 @@
       <c r="Q3" t="inlineStr">
         <is>
           <t>执行前及施法过程中阻断本技能的结果标志 ID，多个用逗号分隔；空表示不检查。</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>?????????????? VFX ID?0 ????????</t>
         </is>
       </c>
     </row>
@@ -787,6 +802,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -840,6 +858,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -874,7 +895,7 @@
       </c>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -892,6 +913,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R6" t="n">
+        <v>90001002</v>
       </c>
     </row>
     <row r="7">
@@ -927,7 +951,7 @@
       </c>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -945,6 +969,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R7" t="n">
+        <v>90001001</v>
       </c>
     </row>
     <row r="8">
@@ -999,6 +1026,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R8" t="n">
+        <v>90001003</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1052,6 +1082,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1105,6 +1138,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R10" t="n">
+        <v>90002001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1158,6 +1194,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R11" t="n">
+        <v>90002002</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1192,7 +1231,7 @@
       </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1210,6 +1249,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R12" t="n">
+        <v>90002003</v>
       </c>
     </row>
     <row r="13">
@@ -1264,6 +1306,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1317,6 +1362,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R14" t="n">
+        <v>90003001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1370,6 +1418,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R15" t="n">
+        <v>90003002</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1423,6 +1474,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R16" t="n">
+        <v>90003003</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1476,6 +1530,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1510,7 +1567,7 @@
       </c>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
@@ -1528,6 +1585,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R18" t="n">
+        <v>90004001</v>
       </c>
     </row>
     <row r="19">
@@ -1582,6 +1642,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1635,6 +1698,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R20" t="n">
+        <v>90004002</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1669,7 +1735,7 @@
       </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -1687,6 +1753,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R21" t="n">
+        <v>90004003</v>
       </c>
     </row>
     <row r="22">
@@ -1741,6 +1810,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1794,6 +1866,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R23" t="n">
+        <v>90005001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1830,7 +1905,7 @@
         <v>50050201</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1845,6 +1920,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R24" t="n">
+        <v>90005002</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1879,7 +1957,7 @@
       </c>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -1897,6 +1975,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R25" t="n">
+        <v>90005003</v>
       </c>
     </row>
     <row r="26">
@@ -1951,6 +2032,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2004,6 +2088,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R27" t="n">
+        <v>90006001</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2057,6 +2144,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R28" t="n">
+        <v>90006002</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2110,6 +2200,9 @@
           <t>3</t>
         </is>
       </c>
+      <c r="R29" t="n">
+        <v>90006003</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2163,6 +2256,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2197,7 +2293,7 @@
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -2215,6 +2311,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R31" t="n">
+        <v>90007001</v>
       </c>
     </row>
     <row r="32">
@@ -2250,7 +2349,7 @@
       </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2268,6 +2367,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R32" t="n">
+        <v>90007002</v>
       </c>
     </row>
     <row r="33">
@@ -2303,7 +2405,7 @@
       </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2321,6 +2423,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R33" t="n">
+        <v>90007004</v>
       </c>
     </row>
     <row r="34">
@@ -2373,6 +2478,9 @@
       <c r="Q34" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2426,6 +2534,9 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2460,7 +2571,7 @@
       </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2478,6 +2589,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R36" t="n">
+        <v>90008002</v>
       </c>
     </row>
     <row r="37">
@@ -2513,7 +2627,7 @@
       </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2531,6 +2645,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R37" t="n">
+        <v>90008004</v>
       </c>
     </row>
     <row r="38">
@@ -2566,7 +2683,7 @@
       </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -2584,6 +2701,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R38" t="n">
+        <v>90008006</v>
       </c>
     </row>
     <row r="39">
@@ -2637,6 +2757,9 @@
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2651,7 +2774,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -2987,7 +3110,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10080002,10080003</t>
+          <t>10080002,10080003,10080005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3009,7 +3132,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -4982,12 +5105,12 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>300,0.6,3.5,250,1000</t>
+          <t>300,0.6,3.5,250,2000</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>damage,physicalAttackRatio,radius,delayMs,stunDurationMs</t>
+          <t>damage,physicalAttackRatio,radius,delayMs,slowDurationMs</t>
         </is>
       </c>
       <c r="G97" s="4" t="n"/>
@@ -5030,7 +5153,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>1008,5000,5000,3</t>
+          <t>1008,1000,14000,14</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -5082,7 +5205,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>

--- a/LubanConfig/Moba/Production/Datas/J-技能表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-技能表.xlsx
@@ -452,8 +452,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:S39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -565,6 +565,11 @@
           <t>PreviewVfxId</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>AllowCastWithoutTarget</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -657,6 +662,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -747,6 +757,11 @@
       <c r="R3" t="inlineStr">
         <is>
           <t>?????????????? VFX ID?0 ????????</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>无有效目标时是否允许按瞄准方向空放。</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1928,7 @@
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
@@ -2523,11 +2538,7 @@
         </is>
       </c>
       <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>RequiredTargetQueryId</t>
-        </is>
-      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
@@ -2536,6 +2547,9 @@
       </c>
       <c r="R35" t="n">
         <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2774,7 +2788,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -3132,7 +3146,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -5205,7 +5219,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
